--- a/data/은행지수.xlsx
+++ b/data/은행지수.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4338"/>
+  <dimension ref="A1:C4339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48107,74 +48107,69 @@
       <c r="A4334" s="2" t="n">
         <v>45488</v>
       </c>
-      <c r="B4334" t="inlineStr">
-        <is>
-          <t>855.73</t>
-        </is>
-      </c>
-      <c r="C4334" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
+      <c r="B4334" t="n">
+        <v>855.73</v>
+      </c>
+      <c r="C4334" t="n">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="4335">
       <c r="A4335" s="2" t="n">
         <v>45489</v>
       </c>
-      <c r="B4335" t="inlineStr">
-        <is>
-          <t>854.59</t>
-        </is>
-      </c>
-      <c r="C4335" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
+      <c r="B4335" t="n">
+        <v>854.59</v>
+      </c>
+      <c r="C4335" t="n">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="4336">
       <c r="A4336" s="2" t="n">
         <v>45490</v>
       </c>
-      <c r="B4336" t="inlineStr">
-        <is>
-          <t>860.13</t>
-        </is>
-      </c>
-      <c r="C4336" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="B4336" t="n">
+        <v>860.13</v>
+      </c>
+      <c r="C4336" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="4337">
       <c r="A4337" s="2" t="n">
         <v>45491</v>
       </c>
-      <c r="B4337" t="inlineStr">
-        <is>
-          <t>863.34</t>
-        </is>
-      </c>
-      <c r="C4337" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+      <c r="B4337" t="n">
+        <v>863.34</v>
+      </c>
+      <c r="C4337" t="n">
+        <v>0.37</v>
       </c>
     </row>
     <row r="4338">
       <c r="A4338" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B4338" t="inlineStr">
+      <c r="B4338" t="n">
+        <v>863.05</v>
+      </c>
+      <c r="C4338" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="4339">
+      <c r="A4339" s="2" t="n">
+        <v>45495</v>
+      </c>
+      <c r="B4339" t="inlineStr">
         <is>
-          <t>863.05</t>
+          <t>875.01</t>
         </is>
       </c>
-      <c r="C4338" t="inlineStr">
+      <c r="C4339" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>1.39</t>
         </is>
       </c>
     </row>
